--- a/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.1_Retention_Deletion_Triggers_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.1_Retention_Deletion_Triggers_20260208.xlsx
@@ -943,7 +943,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>• NIST SP 800-88 Rev. 1: Guidelines for Media Sanitization (reference only)</t>
+          <t>• NIST SP 800-88 Rev. 2: Guidelines for Media Sanitization (reference only)</t>
         </is>
       </c>
     </row>
